--- a/data/trans_dic/P0901-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,98</t>
+          <t>1,81; 5,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,09</t>
+          <t>2,44; 6,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,92</t>
+          <t>0,92; 3,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,26</t>
+          <t>0,5; 6,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,64</t>
+          <t>3,45; 7,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,23</t>
+          <t>2,91; 7,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,74</t>
+          <t>1,89; 5,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,07</t>
+          <t>1,39; 7,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,42</t>
+          <t>3,0; 5,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,06</t>
+          <t>3,06; 5,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,08</t>
+          <t>1,63; 3,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,53</t>
+          <t>1,39; 5,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,6</t>
+          <t>1,84; 4,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,18</t>
+          <t>2,27; 5,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,41</t>
+          <t>2,99; 6,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,8</t>
+          <t>4,69; 11,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,39</t>
+          <t>6,11; 10,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,02</t>
+          <t>3,31; 7,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,32</t>
+          <t>4,27; 8,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,25</t>
+          <t>2,8; 7,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,82</t>
+          <t>4,21; 6,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,45</t>
+          <t>3,1; 5,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,73</t>
+          <t>4,02; 6,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,85</t>
+          <t>4,19; 8,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,81</t>
+          <t>3,38; 6,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,56</t>
+          <t>4,75; 8,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,16</t>
+          <t>2,88; 6,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 10,91</t>
+          <t>5,95; 10,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,6</t>
+          <t>7,13; 11,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 14,63</t>
+          <t>9,7; 14,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,35</t>
+          <t>6,83; 11,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,94</t>
+          <t>8,61; 13,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,63</t>
+          <t>5,72; 8,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,04</t>
+          <t>7,61; 11,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,18</t>
+          <t>5,18; 7,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,41</t>
+          <t>7,92; 11,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,77</t>
+          <t>5,12; 9,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,68</t>
+          <t>6,7; 11,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 13,08</t>
+          <t>7,89; 13,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,71</t>
+          <t>4,17; 14,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 17,58</t>
+          <t>11,22; 17,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,97; 18,88</t>
+          <t>12,77; 18,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,98; 16,54</t>
+          <t>10,88; 16,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 18,94</t>
+          <t>13,26; 18,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,8</t>
+          <t>8,98; 12,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 14,32</t>
+          <t>10,42; 14,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,7</t>
+          <t>10,2; 13,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 15,38</t>
+          <t>7,83; 15,71</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 19,95</t>
+          <t>12,21; 19,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,79; 20,14</t>
+          <t>12,72; 19,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 17,29</t>
+          <t>10,16; 17,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,2; 23,85</t>
+          <t>17,26; 24,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,52; 22,11</t>
+          <t>14,43; 22,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,42; 33,47</t>
+          <t>25,15; 33,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,57; 28,92</t>
+          <t>20,53; 28,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,72; 27,23</t>
+          <t>21,76; 27,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,82</t>
+          <t>14,15; 19,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,09; 25,96</t>
+          <t>19,86; 25,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,29; 21,97</t>
+          <t>16,32; 21,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,29; 24,68</t>
+          <t>20,21; 24,79</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,1; 23,26</t>
+          <t>14,23; 22,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,71; 32,54</t>
+          <t>20,8; 31,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,72</t>
+          <t>15,05; 23,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,49; 20,93</t>
+          <t>14,93; 21,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,91; 38,54</t>
+          <t>29,1; 38,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,46; 45,55</t>
+          <t>34,66; 44,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,3; 43,95</t>
+          <t>32,57; 43,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,02; 30,62</t>
+          <t>8,49; 30,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,39; 30,14</t>
+          <t>23,27; 30,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,74; 37,46</t>
+          <t>29,77; 37,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,85; 32,82</t>
+          <t>25,55; 32,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 24,73</t>
+          <t>9,84; 24,68</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,57; 42,5</t>
+          <t>30,09; 42,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,44; 54,52</t>
+          <t>41,3; 54,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,55; 43,83</t>
+          <t>32,78; 43,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,54; 40,1</t>
+          <t>30,84; 39,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,55; 51,01</t>
+          <t>39,08; 50,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,13; 67,19</t>
+          <t>56,79; 66,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,22; 63,22</t>
+          <t>52,6; 63,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,5; 59,56</t>
+          <t>52,33; 59,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,23; 46,57</t>
+          <t>37,59; 46,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52,42; 60,54</t>
+          <t>52,2; 60,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,26; 54,58</t>
+          <t>46,0; 54,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,85; 50,36</t>
+          <t>45,02; 50,3</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,07; 10,11</t>
+          <t>8,08; 10,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,01; 13,2</t>
+          <t>10,89; 13,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,49; 11,57</t>
+          <t>9,52; 11,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,55</t>
+          <t>9,95; 14,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,01; 17,65</t>
+          <t>15,11; 17,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,09</t>
+          <t>19,41; 22,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 20,89</t>
+          <t>18,04; 20,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,78</t>
+          <t>15,48; 20,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,96; 13,66</t>
+          <t>11,95; 13,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,63; 17,46</t>
+          <t>15,6; 17,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,15; 15,96</t>
+          <t>14,23; 15,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,09; 17,3</t>
+          <t>13,91; 17,4</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9334; 24627</t>
+          <t>8950; 26855</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10858; 27671</t>
+          <t>11090; 28674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3823; 16448</t>
+          <t>3843; 16327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1882; 25025</t>
+          <t>1985; 25107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16220; 35731</t>
+          <t>16136; 35099</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12902; 31108</t>
+          <t>12532; 31088</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7687; 22699</t>
+          <t>7496; 20933</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5028; 28403</t>
+          <t>4350; 24368</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30151; 52154</t>
+          <t>28844; 53687</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27588; 53552</t>
+          <t>27071; 51701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14482; 33230</t>
+          <t>13299; 32021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9404; 39470</t>
+          <t>9910; 39111</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14426; 33811</t>
+          <t>13544; 32582</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15477; 35573</t>
+          <t>15569; 35257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17344; 37853</t>
+          <t>17678; 38515</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19687; 45722</t>
+          <t>19856; 47705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37578; 65017</t>
+          <t>38248; 66212</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21098; 42823</t>
+          <t>20226; 42726</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24244; 46913</t>
+          <t>24085; 49068</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12013; 37029</t>
+          <t>14306; 36588</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57725; 92873</t>
+          <t>57348; 93116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40621; 70747</t>
+          <t>40212; 72126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46516; 77717</t>
+          <t>46387; 77215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38800; 73316</t>
+          <t>39168; 76006</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21540; 43523</t>
+          <t>21579; 42560</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32160; 58374</t>
+          <t>32414; 57809</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19324; 41217</t>
+          <t>19267; 41046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31632; 58538</t>
+          <t>31912; 58965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49310; 80017</t>
+          <t>49195; 79875</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67518; 104008</t>
+          <t>68986; 104732</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45822; 75038</t>
+          <t>45167; 77194</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46698; 70204</t>
+          <t>46728; 70545</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77378; 114631</t>
+          <t>75952; 115973</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107939; 153699</t>
+          <t>106042; 153131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69335; 108824</t>
+          <t>68940; 106270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84574; 123071</t>
+          <t>85417; 120196</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25963; 50704</t>
+          <t>26576; 50389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40965; 71800</t>
+          <t>41155; 71401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51325; 84533</t>
+          <t>50944; 85207</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37627; 130443</t>
+          <t>37011; 128002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58504; 90661</t>
+          <t>57852; 88938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79893; 116319</t>
+          <t>78681; 115928</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71255; 107371</t>
+          <t>70602; 104202</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95062; 134881</t>
+          <t>94415; 133066</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93153; 132461</t>
+          <t>92884; 131093</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127230; 176202</t>
+          <t>128307; 175699</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130985; 177452</t>
+          <t>132141; 180721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>113971; 245969</t>
+          <t>125135; 251270</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47840; 77163</t>
+          <t>47234; 74947</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54943; 86490</t>
+          <t>54628; 84920</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50263; 82654</t>
+          <t>48556; 81761</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96543; 133842</t>
+          <t>96853; 135026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58679; 89304</t>
+          <t>58293; 90253</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109333; 149874</t>
+          <t>112612; 150816</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>102179; 143683</t>
+          <t>101990; 140783</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>118991; 149198</t>
+          <t>119197; 148921</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>115165; 156733</t>
+          <t>111878; 154987</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>176255; 227690</t>
+          <t>174255; 224813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158817; 214113</t>
+          <t>159093; 212031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>225038; 273789</t>
+          <t>224126; 274964</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41261; 68064</t>
+          <t>41639; 66903</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67245; 100804</t>
+          <t>64424; 98803</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50563; 79312</t>
+          <t>50303; 79940</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53248; 76954</t>
+          <t>54889; 78077</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>99142; 132154</t>
+          <t>99781; 133140</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>121983; 161228</t>
+          <t>122683; 159259</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>125804; 166010</t>
+          <t>123050; 163785</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48819; 186301</t>
+          <t>51643; 186344</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148643; 191527</t>
+          <t>147883; 190885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>197382; 248623</t>
+          <t>197625; 245631</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>184075; 233702</t>
+          <t>181906; 232334</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>96404; 241358</t>
+          <t>96038; 240906</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>62060; 89203</t>
+          <t>63161; 89831</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>103550; 136215</t>
+          <t>103184; 136394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83659; 112650</t>
+          <t>84233; 111517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86206; 113174</t>
+          <t>87044; 112568</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>132076; 170323</t>
+          <t>130501; 169375</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>222230; 261352</t>
+          <t>220897; 260089</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>208962; 252980</t>
+          <t>210501; 254587</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>223349; 253383</t>
+          <t>222616; 252260</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>202481; 253249</t>
+          <t>204419; 251299</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>334867; 386776</t>
+          <t>333455; 385157</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>304013; 358668</t>
+          <t>302304; 357725</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>317401; 356389</t>
+          <t>318604; 355923</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>264385; 331126</t>
+          <t>264894; 336158</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>377124; 452238</t>
+          <t>373017; 456133</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>322135; 392663</t>
+          <t>323257; 393536</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>356462; 503192</t>
+          <t>344105; 500524</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>507095; 596362</t>
+          <t>510656; 594358</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>692353; 785922</t>
+          <t>690758; 793204</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>641640; 740543</t>
+          <t>639480; 736634</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>559095; 760672</t>
+          <t>566674; 762632</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>795998; 909314</t>
+          <t>795588; 900460</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1091513; 1219392</t>
+          <t>1089810; 1217156</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>981712; 1107494</t>
+          <t>987151; 1107887</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1003297; 1231605</t>
+          <t>990136; 1238738</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0901-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,44</t>
+          <t>1,79; 4,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,31</t>
+          <t>2,65; 6,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,89</t>
+          <t>0,93; 4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,28</t>
+          <t>0,36; 5,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,51</t>
+          <t>3,39; 7,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,23</t>
+          <t>2,97; 7,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,29</t>
+          <t>1,86; 5,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,78</t>
+          <t>2,26; 9,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,58</t>
+          <t>3,05; 5,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,85</t>
+          <t>3,13; 6,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,93</t>
+          <t>1,68; 3,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,48</t>
+          <t>1,64; 5,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,43</t>
+          <t>1,94; 4,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,13</t>
+          <t>2,37; 5,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,52</t>
+          <t>2,94; 6,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,26</t>
+          <t>4,27; 10,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,59</t>
+          <t>6,16; 10,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,0</t>
+          <t>3,28; 7,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,71</t>
+          <t>4,22; 8,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,16</t>
+          <t>3,47; 7,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,84</t>
+          <t>4,31; 6,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,56</t>
+          <t>3,18; 5,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,69</t>
+          <t>3,96; 6,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,13</t>
+          <t>4,41; 7,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,66</t>
+          <t>3,35; 6,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,48</t>
+          <t>4,85; 8,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,13</t>
+          <t>2,91; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,99</t>
+          <t>5,28; 9,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,58</t>
+          <t>7,17; 11,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,73</t>
+          <t>9,28; 14,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,67</t>
+          <t>6,85; 11,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 13,0</t>
+          <t>8,4; 12,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 8,73</t>
+          <t>5,7; 8,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,0</t>
+          <t>7,71; 10,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,99</t>
+          <t>5,29; 8,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,14</t>
+          <t>7,39; 10,62</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,71</t>
+          <t>5,24; 9,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,62</t>
+          <t>6,77; 11,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 13,19</t>
+          <t>8,24; 13,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 14,44</t>
+          <t>10,99; 16,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 17,25</t>
+          <t>11,22; 17,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,81</t>
+          <t>12,66; 18,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,05</t>
+          <t>10,83; 16,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 18,68</t>
+          <t>14,09; 18,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,67</t>
+          <t>8,83; 12,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,28</t>
+          <t>10,42; 14,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 13,95</t>
+          <t>10,07; 14,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,71</t>
+          <t>13,22; 16,76</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 19,38</t>
+          <t>12,32; 19,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,72; 19,78</t>
+          <t>13,07; 20,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 17,11</t>
+          <t>9,98; 16,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,26; 24,06</t>
+          <t>16,84; 23,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 22,34</t>
+          <t>14,51; 22,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,15; 33,68</t>
+          <t>25,1; 33,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 28,34</t>
+          <t>20,35; 28,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,76; 27,18</t>
+          <t>22,45; 27,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 19,6</t>
+          <t>14,5; 19,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,86; 25,63</t>
+          <t>20,14; 25,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,75</t>
+          <t>16,31; 21,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,21; 24,79</t>
+          <t>20,23; 24,58</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,23; 22,87</t>
+          <t>14,34; 23,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,8; 31,89</t>
+          <t>21,12; 32,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,05; 23,91</t>
+          <t>15,06; 23,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,93; 21,24</t>
+          <t>14,24; 20,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,1; 38,82</t>
+          <t>28,94; 39,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,66; 44,99</t>
+          <t>34,04; 44,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,57; 43,36</t>
+          <t>32,8; 43,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 30,63</t>
+          <t>26,66; 33,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,27; 30,04</t>
+          <t>23,33; 30,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,77; 37,0</t>
+          <t>29,96; 37,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,55; 32,63</t>
+          <t>25,84; 32,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 24,68</t>
+          <t>21,58; 26,08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,09; 42,8</t>
+          <t>30,1; 42,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,3; 54,59</t>
+          <t>41,42; 54,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,78; 43,39</t>
+          <t>32,81; 43,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,84; 39,88</t>
+          <t>30,73; 40,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,08; 50,73</t>
+          <t>39,34; 50,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,79; 66,86</t>
+          <t>56,58; 67,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,6; 63,62</t>
+          <t>52,23; 63,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,33; 59,3</t>
+          <t>53,31; 60,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,59; 46,21</t>
+          <t>37,74; 46,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52,2; 60,29</t>
+          <t>52,18; 60,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,0; 54,43</t>
+          <t>45,84; 54,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,02; 50,3</t>
+          <t>45,24; 50,85</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,08; 10,26</t>
+          <t>8,13; 10,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,31</t>
+          <t>10,88; 13,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,59</t>
+          <t>9,42; 11,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,95; 14,48</t>
+          <t>12,41; 14,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,11; 17,59</t>
+          <t>15,08; 17,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,41; 22,29</t>
+          <t>19,51; 22,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,04; 20,78</t>
+          <t>17,92; 20,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,48; 20,83</t>
+          <t>19,68; 21,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,95; 13,53</t>
+          <t>11,95; 13,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,6; 17,43</t>
+          <t>15,63; 17,44</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,23; 15,97</t>
+          <t>14,07; 15,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,91; 17,4</t>
+          <t>16,45; 18,23</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>25433</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8950; 26855</t>
+          <t>8845; 24071</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11090; 28674</t>
+          <t>12014; 29654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3843; 16327</t>
+          <t>3922; 16759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1985; 25107</t>
+          <t>1481; 22218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16136; 35099</t>
+          <t>15829; 34289</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12532; 31088</t>
+          <t>12797; 30257</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7496; 20933</t>
+          <t>7347; 21920</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4350; 24368</t>
+          <t>8185; 35487</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28844; 53687</t>
+          <t>29346; 55328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27071; 51701</t>
+          <t>27723; 53082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13299; 32021</t>
+          <t>13714; 32258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9910; 39111</t>
+          <t>12664; 43729</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>58837</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13544; 32582</t>
+          <t>14294; 33469</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15569; 35257</t>
+          <t>16262; 35442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17678; 38515</t>
+          <t>17381; 38188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19856; 47705</t>
+          <t>20343; 47926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38248; 66212</t>
+          <t>38524; 65954</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20226; 42726</t>
+          <t>20004; 43164</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24085; 49068</t>
+          <t>23789; 46262</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14306; 36588</t>
+          <t>17364; 38770</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57348; 93116</t>
+          <t>58664; 94331</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40212; 72126</t>
+          <t>41279; 70664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46387; 77215</t>
+          <t>45672; 77829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39168; 76006</t>
+          <t>43090; 78031</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>64982</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>110529</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21579; 42560</t>
+          <t>21370; 44080</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32414; 57809</t>
+          <t>33040; 60852</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19267; 41046</t>
+          <t>19461; 39456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31912; 58965</t>
+          <t>32794; 61494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49195; 79875</t>
+          <t>49476; 79798</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68986; 104732</t>
+          <t>65987; 103677</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45167; 77194</t>
+          <t>45310; 75275</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46728; 70545</t>
+          <t>52264; 78715</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75952; 115973</t>
+          <t>75667; 114098</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106042; 153131</t>
+          <t>107384; 151286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68940; 106270</t>
+          <t>70438; 109519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85417; 120196</t>
+          <t>91813; 132031</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86878</t>
+          <t>94984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>112849</t>
+          <t>119594</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>199726</t>
+          <t>214577</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26576; 50389</t>
+          <t>27216; 50482</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41155; 71401</t>
+          <t>41603; 70553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50944; 85207</t>
+          <t>53261; 84653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37011; 128002</t>
+          <t>76909; 116390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57852; 88938</t>
+          <t>57844; 89587</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78681; 115928</t>
+          <t>78037; 116762</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70602; 104202</t>
+          <t>70325; 105391</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94415; 133066</t>
+          <t>103715; 137560</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92884; 131093</t>
+          <t>91413; 131588</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128307; 175699</t>
+          <t>128261; 173873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132141; 180721</t>
+          <t>130378; 181433</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>125135; 251270</t>
+          <t>189741; 240568</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114630</t>
+          <t>120550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>152034</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>248687</t>
+          <t>272585</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47234; 74947</t>
+          <t>47640; 75352</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54628; 84920</t>
+          <t>56124; 86229</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48556; 81761</t>
+          <t>47692; 80117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96853; 135026</t>
+          <t>102643; 140285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58293; 90253</t>
+          <t>58612; 88894</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112612; 150816</t>
+          <t>112408; 151639</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>101990; 140783</t>
+          <t>101123; 139935</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>119197; 148921</t>
+          <t>136673; 167815</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111878; 154987</t>
+          <t>114659; 154425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>174255; 224813</t>
+          <t>176672; 227638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159093; 212031</t>
+          <t>158969; 210051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>224126; 274964</t>
+          <t>246423; 299435</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65149</t>
+          <t>70172</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>119537</t>
+          <t>131175</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>184686</t>
+          <t>201347</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41639; 66903</t>
+          <t>41943; 68265</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64424; 98803</t>
+          <t>65433; 99952</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50303; 79940</t>
+          <t>50345; 77851</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54889; 78077</t>
+          <t>57886; 84962</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>99781; 133140</t>
+          <t>99249; 134671</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>122683; 159259</t>
+          <t>120501; 158444</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>123050; 163785</t>
+          <t>123910; 163155</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51643; 186344</t>
+          <t>117061; 145352</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>147883; 190885</t>
+          <t>148284; 190710</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>197625; 245631</t>
+          <t>198873; 247327</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181906; 232334</t>
+          <t>183996; 234724</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>96038; 240906</t>
+          <t>182475; 220588</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>109480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>237673</t>
+          <t>262248</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>336990</t>
+          <t>371728</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>63161; 89831</t>
+          <t>63181; 89251</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>103184; 136394</t>
+          <t>103491; 136589</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84233; 111517</t>
+          <t>84328; 112461</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87044; 112568</t>
+          <t>95185; 124856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>130501; 169375</t>
+          <t>131350; 169061</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>220897; 260089</t>
+          <t>220094; 261782</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>210501; 254587</t>
+          <t>208992; 253186</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>222616; 252260</t>
+          <t>247444; 279219</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>204419; 251299</t>
+          <t>205240; 251697</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>333455; 385157</t>
+          <t>333324; 388859</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>302304; 357725</t>
+          <t>301262; 359040</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>318604; 355923</t>
+          <t>350094; 393483</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>448719</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>774032</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1146752</t>
+          <t>1255035</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>264894; 336158</t>
+          <t>266224; 332220</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>373017; 456133</t>
+          <t>372736; 457774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>323257; 393536</t>
+          <t>319716; 394196</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>344105; 500524</t>
+          <t>438177; 522614</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>510656; 594358</t>
+          <t>509670; 596973</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>690758; 793204</t>
+          <t>694203; 793882</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>639480; 736634</t>
+          <t>635291; 741820</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>566674; 762632</t>
+          <t>734684; 817138</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>795588; 900460</t>
+          <t>795572; 901563</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1089810; 1217156</t>
+          <t>1091529; 1218293</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>987151; 1107887</t>
+          <t>976514; 1106741</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>990136; 1238738</t>
+          <t>1194796; 1324056</t>
         </is>
       </c>
     </row>
